--- a/A.先启阶段/4.项目分工与进度.xlsx
+++ b/A.先启阶段/4.项目分工与进度.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HHH\Desktop\学生提交材料\3-小组实训作品\组号-项目名称-实训项目成果\A.先启阶段\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HHH\Desktop\学生提交材料\aiagent\A.先启阶段\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E61BBE0-5AF7-4EF5-9237-CEBC7EBDA47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2AB6B84-7E25-4484-AAF1-15DF5BF18D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-101" yWindow="-101" windowWidth="25981" windowHeight="15589" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2608" yWindow="2608" windowWidth="19334" windowHeight="11248" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="47">
   <si>
     <t>先启阶段</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -166,13 +166,24 @@
   </si>
   <si>
     <t>算法</t>
+  </si>
+  <si>
+    <t>完成情况</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>√</t>
+  </si>
+  <si>
+    <t>√</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,6 +224,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -240,7 +258,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -271,6 +289,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -566,7 +587,7 @@
     <col min="1" max="1" width="8.5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="8.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.4140625" style="1" customWidth="1"/>
     <col min="7" max="7" width="2.1640625" style="1" customWidth="1"/>
     <col min="8" max="17" width="7.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="16384" width="9.08203125" style="1"/>
@@ -586,7 +607,9 @@
       <c r="E3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="G3" s="3"/>
       <c r="H3" s="4">
         <v>46213</v>
@@ -635,7 +658,9 @@
       <c r="E4" s="7">
         <v>46213</v>
       </c>
-      <c r="F4" s="8"/>
+      <c r="F4" s="11" t="s">
+        <v>46</v>
+      </c>
       <c r="G4" s="8"/>
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
@@ -656,7 +681,9 @@
       <c r="E5" s="7">
         <v>46221</v>
       </c>
-      <c r="F5" s="8"/>
+      <c r="F5" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G5" s="8"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
@@ -677,7 +704,9 @@
       <c r="E6" s="7">
         <v>46219</v>
       </c>
-      <c r="F6" s="8"/>
+      <c r="F6" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G6" s="8"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
@@ -698,7 +727,9 @@
       <c r="E7" s="7">
         <v>46219</v>
       </c>
-      <c r="F7" s="8"/>
+      <c r="F7" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G7" s="8"/>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
@@ -719,7 +750,9 @@
       <c r="E8" s="7">
         <v>46219</v>
       </c>
-      <c r="F8" s="8"/>
+      <c r="F8" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
@@ -740,7 +773,9 @@
       <c r="E9" s="7">
         <v>46213</v>
       </c>
-      <c r="F9" s="8"/>
+      <c r="F9" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
@@ -761,7 +796,9 @@
       <c r="E10" s="7">
         <v>46213</v>
       </c>
-      <c r="F10" s="8"/>
+      <c r="F10" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G10" s="8"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
@@ -782,7 +819,9 @@
       <c r="E11" s="7">
         <v>46213</v>
       </c>
-      <c r="F11" s="8"/>
+      <c r="F11" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G11" s="8"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
@@ -803,7 +842,9 @@
       <c r="E12" s="7">
         <v>46213</v>
       </c>
-      <c r="F12" s="8"/>
+      <c r="F12" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G12" s="8"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
@@ -826,7 +867,9 @@
       <c r="E13" s="7">
         <v>46215</v>
       </c>
-      <c r="F13" s="8"/>
+      <c r="F13" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G13" s="8"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
@@ -847,7 +890,9 @@
       <c r="E14" s="7">
         <v>46215</v>
       </c>
-      <c r="F14" s="8"/>
+      <c r="F14" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G14" s="8"/>
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
@@ -868,7 +913,9 @@
       <c r="E15" s="7">
         <v>46215</v>
       </c>
-      <c r="F15" s="8"/>
+      <c r="F15" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G15" s="8"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
@@ -889,7 +936,9 @@
       <c r="E16" s="7">
         <v>46215</v>
       </c>
-      <c r="F16" s="8"/>
+      <c r="F16" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G16" s="8"/>
       <c r="H16" s="9"/>
       <c r="I16" s="9"/>
@@ -910,7 +959,9 @@
       <c r="E17" s="7">
         <v>46215</v>
       </c>
-      <c r="F17" s="8"/>
+      <c r="F17" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G17" s="8"/>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
@@ -931,7 +982,9 @@
       <c r="E18" s="7">
         <v>46215</v>
       </c>
-      <c r="F18" s="8"/>
+      <c r="F18" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G18" s="8"/>
       <c r="H18" s="9"/>
       <c r="I18" s="9"/>
@@ -952,7 +1005,9 @@
       <c r="E19" s="7">
         <v>46215</v>
       </c>
-      <c r="F19" s="8"/>
+      <c r="F19" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G19" s="8"/>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
@@ -975,7 +1030,9 @@
       <c r="E20" s="7">
         <v>46218</v>
       </c>
-      <c r="F20" s="8"/>
+      <c r="F20" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G20" s="8"/>
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
@@ -996,7 +1053,9 @@
       <c r="E21" s="7">
         <v>46218</v>
       </c>
-      <c r="F21" s="8"/>
+      <c r="F21" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G21" s="8"/>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
@@ -1017,7 +1076,9 @@
       <c r="E22" s="7">
         <v>46218</v>
       </c>
-      <c r="F22" s="8"/>
+      <c r="F22" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G22" s="8"/>
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
@@ -1038,7 +1099,9 @@
       <c r="E23" s="7">
         <v>46217</v>
       </c>
-      <c r="F23" s="8"/>
+      <c r="F23" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G23" s="8"/>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
@@ -1059,7 +1122,9 @@
       <c r="E24" s="7">
         <v>46217</v>
       </c>
-      <c r="F24" s="8"/>
+      <c r="F24" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G24" s="8"/>
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
@@ -1080,7 +1145,9 @@
       <c r="E25" s="7">
         <v>46218</v>
       </c>
-      <c r="F25" s="8"/>
+      <c r="F25" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G25" s="8"/>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
@@ -1101,7 +1168,9 @@
       <c r="E26" s="7">
         <v>46218</v>
       </c>
-      <c r="F26" s="8"/>
+      <c r="F26" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G26" s="8"/>
       <c r="H26" s="9"/>
       <c r="I26" s="9"/>
@@ -1122,7 +1191,9 @@
       <c r="E27" s="7">
         <v>46219</v>
       </c>
-      <c r="F27" s="8"/>
+      <c r="F27" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G27" s="8"/>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
@@ -1143,7 +1214,9 @@
       <c r="E28" s="7">
         <v>46219</v>
       </c>
-      <c r="F28" s="8"/>
+      <c r="F28" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G28" s="8"/>
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
@@ -1164,7 +1237,9 @@
       <c r="E29" s="7">
         <v>46219</v>
       </c>
-      <c r="F29" s="8"/>
+      <c r="F29" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G29" s="8"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
@@ -1183,7 +1258,9 @@
       <c r="E30" s="7">
         <v>46221</v>
       </c>
-      <c r="F30" s="8"/>
+      <c r="F30" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G30" s="8"/>
       <c r="H30" s="9"/>
       <c r="I30" s="9"/>
@@ -1204,7 +1281,9 @@
       <c r="E31" s="7">
         <v>46221</v>
       </c>
-      <c r="F31" s="8"/>
+      <c r="F31" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G31" s="8"/>
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
@@ -1225,7 +1304,9 @@
       <c r="E32" s="7">
         <v>46221</v>
       </c>
-      <c r="F32" s="8"/>
+      <c r="F32" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G32" s="8"/>
       <c r="H32" s="9"/>
       <c r="I32" s="9"/>
@@ -1246,7 +1327,9 @@
       <c r="E33" s="7">
         <v>46221</v>
       </c>
-      <c r="F33" s="8"/>
+      <c r="F33" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G33" s="8"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -1263,7 +1346,9 @@
       <c r="E34" s="7">
         <v>46221</v>
       </c>
-      <c r="F34" s="8"/>
+      <c r="F34" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="G34" s="8"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -1280,7 +1365,9 @@
       <c r="E35" s="7">
         <v>46222</v>
       </c>
-      <c r="F35" s="8"/>
+      <c r="F35" s="11" t="s">
+        <v>46</v>
+      </c>
       <c r="G35" s="8"/>
     </row>
   </sheetData>
